--- a/光伏配储项目/电价数据/2026/拱北站.xlsx
+++ b/光伏配储项目/电价数据/2026/拱北站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5536</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.51776</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.86045</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.12593</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.01936</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.91749</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.7178</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.72726</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.53806</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.59024</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.5236499999999999</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.6896</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.6897300000000001</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.68014</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.5169400000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.6976100000000001</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.66096</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.6861900000000001</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.52665</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.70038</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.54575</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.69847</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.55091</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.73127</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.82074</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.85802</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.67665</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6718099999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45214</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.73373</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.75644</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.00985</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.99429</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.08521</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.75037</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.69785</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.78352</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.94974</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31225</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52303</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7597200000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76761</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74739</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.92799</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.89455</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04781</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.31502</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.12301</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.12162</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.73405</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.21009</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.1689</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09669</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22855</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53472</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.10466</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24723</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47614</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.30498</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23594</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.79945</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.41045</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35398</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28466</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8032899999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16802</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03702</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17642</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5125700000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.61361</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.5138400000000001</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.58793</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.49266</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48599</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.52222</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.50351</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.51363</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.50352</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.50975</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.55867</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.7681</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.0727</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8393400000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.59129</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48497</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.53816</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.5087200000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9349400000000001</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.15069</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.7757999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.1197</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03749</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.98673</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7077100000000001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54786</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.56679</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.67957</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.1537</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.23092</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47495</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15808</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.62902</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.0784</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.81794</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.25104</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13582</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.2831</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62162</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.6383</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57008</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.16079</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16826</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17691</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17146</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.96826</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18758</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.2024</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19404</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66885</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.1614</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20557</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.2104</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.5067</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.41179</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16767</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50946</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26397</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7431</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7648200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91534</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.6029099999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.68451</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6938500000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.53283</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.57752</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.8401000000000001</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.5963200000000001</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.5883200000000001</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.55686</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.5573899999999999</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6343799999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48702</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.58408</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48798</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.5754900000000001</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.52377</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.5569700000000001</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.5119900000000001</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.49821</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.50825</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.46175</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.69274</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8306699999999999</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10787</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.87373</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.74474</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70308</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6043999999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64291</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42517</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7290800000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16424</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.52168</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.67692</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16673</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.62091</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18766</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.16499</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.79273</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.93951</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16388</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.1653</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.89213</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5594600000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47463</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.6742100000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16538</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02833</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.1644</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.39264</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23568</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16568</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21565</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20941</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.40119</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26872</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28567</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64838</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.17134</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17411</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78382</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03895</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07828</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09914</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.08521</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.2044</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16806</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24822</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.9948400000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75422</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.71077</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5301399999999999</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.10962</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.72184</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.71488</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.20079</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.68023</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.85427</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.54069</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.60751</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.22511</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.5931799999999999</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.52444</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.6547500000000001</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.5866699999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.52706</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44338</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.50963</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.5219199999999999</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.57756</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.49535</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.49453</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.45969</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.67631</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.71824</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93263</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16764</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30894</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.83789</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55132</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66578</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90355</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8645</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16384</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43968</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77256</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9530700000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.2047</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.6890499999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12239</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52236</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48519</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6541699999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.99599</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10245</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24896</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16831</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.06095</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.98163</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02564</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.9895900000000001</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.25157</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.44093</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.79298</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34845</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.22994</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.19101</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.8475</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07394</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.16074</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12147</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15383</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.25456</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31802</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15386</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26937</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18763</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18599</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18839</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18903</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17454</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.1521</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.1759</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7238</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5226799999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.72604</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32162</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74358</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49355</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47765</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50449</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.5229400000000001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.71634</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.84762</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.6147100000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70153</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.72658</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.84517</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70502</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55064</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.5496799999999999</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5384099999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59224</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47051</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08524</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26838</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.54987</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48212</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5120800000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46627</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6331100000000001</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5021600000000001</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48317</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48732</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.5942000000000001</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5053799999999999</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.5058</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48596</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34389</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.19082</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9658300000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9816699999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59023</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.6471399999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.5452</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.52876</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.54404</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.51312</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.51188</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.68651</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.5275299999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.5278400000000001</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.51058</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.51142</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.5121599999999999</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26869</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07335</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04534000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08281999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12869</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04697</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04591</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04665999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25318</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26886</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42278</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44589</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.5928600000000001</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.5390499999999999</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.5408500000000001</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.54008</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55686</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27001</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26796</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.74154</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8742300000000001</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.67457</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.64854</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6674099999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7484500000000001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.93924</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48066</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.72987</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73154</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.88776</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.63134</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.53573</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48249</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44904</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08541</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73154</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72812</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6386900000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60287</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.72846</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.78865</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78267</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.60033</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.74166</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01799</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40603</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.84301</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.4338</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29749</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.7885700000000001</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.38051</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04489</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.40078</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76521</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44383</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7743099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8003899999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78503</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8787999999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50198</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41138</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4601</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21849</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54123</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.61622</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.56412</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.57269</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.57929</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.58082</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.56059</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.46919</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.49233</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.48049</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.54203</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.51415</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.51776</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.5143799999999999</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.51435</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.54987</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.5153300000000001</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.47116</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.57169</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56367</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66623</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07968</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.63851</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.56921</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59869</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00136</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33897</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.3066</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27479</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55924</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80174</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57298</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65083</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55055</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.95623</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.77652</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72562</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6420800000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57533</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.9888400000000001</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.9312699999999999</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78851</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.54212</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.67108</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.58905</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.67052</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.6223500000000001</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6631900000000001</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.70414</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.64047</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.66184</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58308</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.57774</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.65986</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.67652</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.62263</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.67027</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.68859</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7611599999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.67933</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.75802</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.68848</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.6861799999999999</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.68772</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.67195</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.66162</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.6197</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.66079</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.6041</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.54315</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.60722</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.5557300000000001</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5804400000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.5571900000000001</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.54259</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.5323</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46854</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57548</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.60885</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62225</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6802</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.53472</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.54848</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.50018</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.52466</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64162</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.5129900000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.6176200000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.72763</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.87125</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.11148</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9320900000000001</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.54498</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11331</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84354</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.94923</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.85917</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.63966</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.80969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06731</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.56951</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52237</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.8749400000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.99472</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.19048</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.78367</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8132999999999999</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.7404299999999999</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7396699999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47512</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44322</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19612</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51259</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.79311</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.74897</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16596</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92134</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64306</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.66713</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7006699999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55486</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16396</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61229</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9091900000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5767599999999999</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.57347</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.33554</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.26005</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.22787</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.34087</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.0073</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.51893</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.60202</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.85894</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50566</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7502000000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07567</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07361</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.98275</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.9363899999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17396</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15409</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.86239</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15537</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60754</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9704299999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01566</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.15478</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.95028</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.9905499999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58455</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.92403</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.98134</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.08889</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.8854299999999999</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.8730599999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79337</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09637</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55555</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.95985</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.99113</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74322</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33169</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.6078300000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.49076</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.49387</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50671</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44528</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.54991</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.5911900000000001</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.4999</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.49389</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.48897</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83305</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71429</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.54928</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.5677000000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.7284700000000001</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.8578</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.56987</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.57399</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.57575</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.51058</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.51033</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.55786</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.61771</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.5611699999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.56977</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.45953</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.46189</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.67716</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54203</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.51049</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.51225</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50574</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.50915</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56811</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.46945</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.57178</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.52865</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.5352100000000001</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.5224299999999999</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.49199</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.51493</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.50205</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.5230399999999999</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.52884</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.5240199999999999</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.48543</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.47282</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5541</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47007</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48514</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7011799999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60294</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6277</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84902</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.2715</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16641</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85221</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45078</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7014199999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.94025</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16798</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12168</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01857</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54188</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.45911</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43903</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43775</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.48482</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.50854</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.58005</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.72142</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.0588</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41364</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.11314</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.99114</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9798600000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9813999999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56587</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54718</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9462999999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08623</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78425</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01325</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76826</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64883</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64156</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70886</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80002</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29848</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.41895</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>1.14167</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.62971</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62426</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.6579</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67128</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66634</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64332</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66781</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20688</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70074</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78254</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.69805</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70582</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71398</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63351</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74827</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02169</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13147</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69188</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70032</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.6941</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77372</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72388</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8132699999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.66662</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.06524</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.46662</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.5799500000000001</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45686</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34415</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.45122</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5999099999999999</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17663</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.47702</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.50152</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.49058</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.5099</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.50201</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.49701</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7471599999999999</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49507</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45218</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92248</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47492</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17985</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90227</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7632100000000001</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44918</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48994</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.44095</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44872</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74676</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42623</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5151399999999999</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68115</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49598</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40559</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45383</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66477</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6517999999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.5235599999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48861</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.48369</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.70485</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.47199</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.44145</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42792</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43921</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51644</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54604</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76149</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76819</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.47999</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54659</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50161</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72315</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76261</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55425</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50184</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02055</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48724</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44691</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09488</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12983</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08379</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11237</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12883</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01863</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19442</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14269</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.1319</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17434</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84138</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.1913</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84845</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34118</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9038200000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73333</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75775</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94901</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.68666</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.39233</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.5575</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.54272</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.53167</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.53727</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75609</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.37198</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.35312</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.5177</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.6160599999999999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.61038</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.53049</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.5127999999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.57714</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.5929099999999999</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.5939800000000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.5179199999999999</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.5884199999999999</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.5324800000000001</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5772699999999999</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.5055500000000001</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46983</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46979</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49951</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45709</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.63858</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54811</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.49969</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.68308</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.02744</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77349</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74124</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27983</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.3413</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71785</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.64134</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.3479</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99479</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59169</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49311</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49461</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5392400000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.58976</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73338</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17692</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.69099</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.9124099999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.66473</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93404</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.88046</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74482</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.7141</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17544</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17663</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.42511</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23624</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.6163</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20465</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28274</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07706</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.39878</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03315</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.6683600000000001</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.6389600000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.13862</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.63326</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47307</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.50526</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45202</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5254800000000001</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5319299999999999</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.8007300000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.66844</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.64964</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50858</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.06799</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66662</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66331</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.79592</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04888</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.16719</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19226</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54601</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15328</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55671</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5717100000000001</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49765</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23462</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47877</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50085</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51128</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43142</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.51546</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.59712</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75636</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12755</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.68912</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.55398</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45896</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41796</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49304</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45492</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44761</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.5806</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47758</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44799</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46204</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46314</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44603</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45965</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46762</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.49423</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48261</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.46227</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.36999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.86194</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.48456</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.43212</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23338</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11176</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.69959</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17353</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09856000000000001</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.6884199999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5588</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49176</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.49535</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42707</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80218</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48432</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09318</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36595</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.8482000000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8061499999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75317</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75179</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51188</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.5541900000000001</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42457</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44192</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.51059</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.7426699999999999</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.57301</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45264</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.75301</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28586</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.28922</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21713</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06141</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.95424</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28434</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.61105</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54444</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5754</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7497999999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54591</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.54115</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21391</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.7527699999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75118</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.57514</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49176</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.98545</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.75946</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61833</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.75034</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17271</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6007400000000001</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.7270700000000001</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62415</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.2365</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.8734299999999999</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.85888</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.88036</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.89896</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15287</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.6387999999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9316</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9565900000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.6197</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.63782</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.73579</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.62018</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79233</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24381</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03402</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.99576</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.00818</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.5145</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.34084</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04806</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7539400000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34523</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5568</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8012400000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5497000000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7509</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7526900000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55903</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46883</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45848</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42189</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62754</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5903200000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5564199999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.53739</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44797</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47341</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49459</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5571499999999999</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81145</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.15359</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11919</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03209</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.1219</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72571</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.72046</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04292</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.0613</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.6684</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5554600000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5619299999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5498500000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47721</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46441</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54637</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54111</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65711</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54164</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04332</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.65411</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54664</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49699</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49753</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48054</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49753</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48033</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57475</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55504</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5585399999999999</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51162</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49839</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.55838</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.65708</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15238</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.05536</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.65831</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5799299999999999</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15084</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.86356</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6575700000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.14024</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.81296</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49241</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.50962</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53284</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34434</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.7103200000000001</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.58113</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.5877100000000001</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.7261299999999999</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.55072</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6257699999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58338</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.62962</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92427</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.96131</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.01027</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.95135</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.9177000000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.94759</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9315</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9148500000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.91718</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.6710499999999999</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.02575</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.6688999999999999</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.02264</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.1245</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10636</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.69892</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.9218</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8426699999999999</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.9095599999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54174</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66677</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68925</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73765</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78772</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.19687</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.07699</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.01649</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32907</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01215</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11123</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91561</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7516900000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.7509400000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.81333</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69177</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69068</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55628</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.68832</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.72461</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6849400000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7469600000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6950599999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46099</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.73307</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5197200000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50546</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43934</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.99442</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.89152</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00773</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.8962899999999999</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01555</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.99838</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.9985700000000001</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.16424</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06779</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.09086</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.6655599999999999</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71796</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.70504</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02566</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69791</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.75093</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13485</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.23092</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.43196</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.20059</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.36268</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.98442</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.40057</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.37984</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.74346</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.65419</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.42169</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.4235</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80747</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.75521</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.8019500000000001</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.55952</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75407</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31354</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00399</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.93411</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9603400000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03398</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.1626</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06211</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86434</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6934400000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22281</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20876</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.20942</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15185</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86761</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09722</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10814</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10817</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.1345</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10587</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52062</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20118</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.6402</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.73161</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.6637799999999999</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18521</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8620399999999999</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06604</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03295</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.05042</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03634</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06918</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12819</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05065</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06126</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18423</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16278</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21615</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20337</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26674</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16946</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14338</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12006</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.1007</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12684</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17656</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19414</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17472</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07729</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6742</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6147</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5658</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5483899999999999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53102</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31365</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31085</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06777</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47914</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51985</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44355</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.43078</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43314</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.44153</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.4382200000000001</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43509</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42837</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41829</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84835</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.56668</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.6840700000000001</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.6997100000000001</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.65135</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.94155</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7525700000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.94692</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15867</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30663</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44583</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43393</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45944</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54607</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.2525</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.8512000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.61974</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73349</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7006100000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50282</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84433</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.2152</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77327</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57994</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58066</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62741</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.70785</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.58351</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7354700000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.61042</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.2001</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17668</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41141</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17806</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17879</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18408</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10398</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07871</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20743</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.1064</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.1927</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05132</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08281</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08294</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54253</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80744</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80411</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5640299999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21386</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84911</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84961</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55457</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56257</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539400000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5477799999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52046</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5575800000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17563</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8829900000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49393</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17168</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50941</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5694600000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8442000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79518</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59699</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85288</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50102</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52288</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54373</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17762</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70099</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5553400000000001</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17397</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54923</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55036</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58077</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79961</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5550700000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7990900000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.84909</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17422</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7986799999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68355</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05243</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17602</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17746</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17538</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8241499999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73256</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6453300000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.67687</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.68488</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73119</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8347899999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6154500000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.80691</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75659</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13684</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.7510599999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60945</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63661</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.63854</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6173</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.6146</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7040299999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6708</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.81399</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70408</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
